--- a/public/sample-data/05-expenditure-detail-FY2026-27-P1-July.xlsx
+++ b/public/sample-data/05-expenditure-detail-FY2026-27-P1-July.xlsx
@@ -79,31 +79,31 @@
     <t>300</t>
   </si>
   <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>6200</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>6300</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>4100</t>
+  </si>
+  <si>
     <t>400</t>
   </si>
   <si>
     <t>9002</t>
   </si>
   <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>6200</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>6300</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
     <t>9700</t>
-  </si>
-  <si>
-    <t>4100</t>
   </si>
   <si>
     <t>3200</t>
@@ -554,16 +554,16 @@
         <v>42000000</v>
       </c>
       <c r="G2">
-        <v>3500000</v>
+        <v>2447910.36</v>
       </c>
       <c r="H2">
-        <v>3500000</v>
+        <v>2447910.36</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>38500000</v>
+        <v>39552089.64</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -586,16 +586,16 @@
         <v>31000000</v>
       </c>
       <c r="G3">
-        <v>2580000</v>
+        <v>1789249.32</v>
       </c>
       <c r="H3">
-        <v>2580000</v>
+        <v>1789249.32</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>28420000</v>
+        <v>29210750.68</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -618,16 +618,16 @@
         <v>22000000</v>
       </c>
       <c r="G4">
-        <v>1830000</v>
+        <v>1257340.92</v>
       </c>
       <c r="H4">
-        <v>1830000</v>
+        <v>1257340.92</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>20170000</v>
+        <v>20742659.08</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -650,16 +650,16 @@
         <v>13500000</v>
       </c>
       <c r="G5">
-        <v>1120000</v>
+        <v>794467.44</v>
       </c>
       <c r="H5">
-        <v>1120000</v>
+        <v>794467.44</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>12380000</v>
+        <v>12705532.56</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -682,16 +682,16 @@
         <v>10000000</v>
       </c>
       <c r="G6">
-        <v>830000</v>
+        <v>582835.8</v>
       </c>
       <c r="H6">
-        <v>830000</v>
+        <v>582835.8</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>9170000</v>
+        <v>9417164.2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -714,16 +714,16 @@
         <v>7000000</v>
       </c>
       <c r="G7">
-        <v>580000</v>
+        <v>396102</v>
       </c>
       <c r="H7">
-        <v>580000</v>
+        <v>396102</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>6420000</v>
+        <v>6603898</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -746,16 +746,16 @@
         <v>12000000</v>
       </c>
       <c r="G8">
-        <v>1000000</v>
+        <v>672241.68</v>
       </c>
       <c r="H8">
-        <v>1000000</v>
+        <v>672241.68</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>11000000</v>
+        <v>11327758.32</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -778,16 +778,16 @@
         <v>4000000</v>
       </c>
       <c r="G9">
-        <v>330000</v>
+        <v>221817.12</v>
       </c>
       <c r="H9">
-        <v>330000</v>
+        <v>221817.12</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>3670000</v>
+        <v>3778182.88</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -810,16 +810,16 @@
         <v>6500000</v>
       </c>
       <c r="G10">
-        <v>540000</v>
+        <v>356774.73</v>
       </c>
       <c r="H10">
-        <v>540000</v>
+        <v>356774.73</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>5960000</v>
+        <v>6143225.27</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -842,16 +842,16 @@
         <v>2000000</v>
       </c>
       <c r="G11">
-        <v>160000</v>
+        <v>108645.12</v>
       </c>
       <c r="H11">
-        <v>160000</v>
+        <v>108645.12</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1840000</v>
+        <v>1891354.88</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -874,16 +874,16 @@
         <v>4000000</v>
       </c>
       <c r="G12">
-        <v>300000</v>
+        <v>208236.48</v>
       </c>
       <c r="H12">
-        <v>300000</v>
+        <v>208236.48</v>
       </c>
       <c r="I12">
-        <v>250000</v>
+        <v>232143</v>
       </c>
       <c r="J12">
-        <v>3450000</v>
+        <v>3559620.52</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -906,16 +906,16 @@
         <v>14000000</v>
       </c>
       <c r="G13">
-        <v>1100000</v>
+        <v>752593.8</v>
       </c>
       <c r="H13">
-        <v>1100000</v>
+        <v>752593.8</v>
       </c>
       <c r="I13">
-        <v>900000</v>
+        <v>835714</v>
       </c>
       <c r="J13">
-        <v>12000000</v>
+        <v>12411692.2</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -923,31 +923,31 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
       </c>
       <c r="F14">
-        <v>8500000</v>
+        <v>3200000</v>
       </c>
       <c r="G14">
-        <v>620000</v>
+        <v>170210.69</v>
       </c>
       <c r="H14">
-        <v>620000</v>
+        <v>170210.69</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="J14">
-        <v>7880000</v>
+        <v>2899789.31</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -955,31 +955,31 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
       </c>
       <c r="F15">
-        <v>3200000</v>
+        <v>4000000</v>
       </c>
       <c r="G15">
-        <v>260000</v>
+        <v>203709.6</v>
       </c>
       <c r="H15">
-        <v>260000</v>
+        <v>203709.6</v>
       </c>
       <c r="I15">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>2800000</v>
+        <v>3796290.4</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -987,31 +987,31 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
       </c>
       <c r="F16">
-        <v>4000000</v>
+        <v>7200000</v>
       </c>
       <c r="G16">
-        <v>330000</v>
+        <v>224080.56</v>
       </c>
       <c r="H16">
-        <v>330000</v>
+        <v>224080.56</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>5385714</v>
       </c>
       <c r="J16">
-        <v>3670000</v>
+        <v>1590205.4400000004</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1019,42 +1019,42 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>14</v>
       </c>
       <c r="F17">
-        <v>7200000</v>
+        <v>5200000</v>
       </c>
       <c r="G17">
-        <v>300000</v>
+        <v>273649.9</v>
       </c>
       <c r="H17">
-        <v>300000</v>
+        <v>273649.9</v>
       </c>
       <c r="I17">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>1100000</v>
+        <v>4926350.1</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
@@ -1063,19 +1063,19 @@
         <v>14</v>
       </c>
       <c r="F18">
-        <v>5200000</v>
+        <v>6400000</v>
       </c>
       <c r="G18">
-        <v>430000</v>
+        <v>354907.39</v>
       </c>
       <c r="H18">
-        <v>430000</v>
+        <v>354907.39</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>4770000</v>
+        <v>6045092.61</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1086,39 +1086,39 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="D19" t="s">
-        <v>19</v>
-      </c>
       <c r="E19" t="s">
         <v>14</v>
       </c>
       <c r="F19">
-        <v>2000000</v>
+        <v>8500000</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>967725</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>967725</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>2000000</v>
+        <v>7532275</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
@@ -1127,19 +1127,19 @@
         <v>14</v>
       </c>
       <c r="F20">
-        <v>6400000</v>
+        <v>2000000</v>
       </c>
       <c r="G20">
-        <v>530000</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>530000</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>5870000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
